--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486332_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486332_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6632</v>
+        <v>5.9928</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0883</v>
+        <v>6.4488</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4251</v>
+        <v>-0.456</v>
       </c>
       <c r="G2" t="n">
         <v>4.2373</v>
@@ -610,13 +610,13 @@
         <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6166</v>
+        <v>-0.2869</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.3245</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0684</v>
+        <v>0.0375</v>
       </c>
       <c r="V2" t="n">
         <v>2.2599</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9294</v>
+        <v>4.3525</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2604</v>
+        <v>5.7759</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.331</v>
+        <v>-1.4234</v>
       </c>
       <c r="G3" t="n">
         <v>2.5751</v>
@@ -688,13 +688,13 @@
         <v>0.87</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6457000000000001</v>
+        <v>-0.2226</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9589</v>
+        <v>-0.4434</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3133</v>
+        <v>0.2208</v>
       </c>
       <c r="V3" t="n">
         <v>1.13</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>S. QUINTELA SALVADOR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9328</v>
+        <v>2.5287</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8263</v>
+        <v>2.2944</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1065</v>
+        <v>0.2343</v>
       </c>
       <c r="G4" t="n">
-        <v>1.044</v>
+        <v>0.8134</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4684</v>
+        <v>-0.5595</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5124</v>
+        <v>1.373</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6497</v>
+        <v>2.0177</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6935</v>
+        <v>0.3713</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9562</v>
+        <v>1.6463</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6057</v>
+        <v>-1.2042</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1619</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5562</v>
+        <v>-0.2733</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7366</v>
+        <v>0.3455</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8736</v>
+        <v>0.2343</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8629</v>
+        <v>0.1111</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3698</v>
+        <v>0.9347</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3904</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.0207</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. DE SOUSA ANJO BRITO</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1197</v>
+        <v>1.9416</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2328</v>
+        <v>1.1125</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1131</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5355</v>
+        <v>1.044</v>
       </c>
       <c r="H5" t="n">
-        <v>1.694</v>
+        <v>-0.4684</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8415</v>
+        <v>1.5124</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6027</v>
+        <v>1.6497</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9564</v>
+        <v>0.6935</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6463</v>
+        <v>0.9562</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0672</v>
+        <v>-0.6057</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2624</v>
+        <v>-1.1619</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8048999999999999</v>
+        <v>0.5562</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6525</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3667</v>
+        <v>0.7453</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8051</v>
+        <v>0.1598</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5615</v>
+        <v>0.5855</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.13</v>
+        <v>0.3698</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13</v>
+        <v>-0.0207</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. QUINTELA SALVADOR</t>
+          <t>D. DE SOUSA ANJO BRITO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4929</v>
+        <v>1.6372</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4436</v>
+        <v>2.966</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0493</v>
+        <v>-1.3289</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8134</v>
+        <v>2.5355</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5595</v>
+        <v>1.694</v>
       </c>
       <c r="I6" t="n">
-        <v>1.373</v>
+        <v>0.8415</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0177</v>
+        <v>4.6027</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3713</v>
+        <v>2.9564</v>
       </c>
       <c r="L6" t="n">
         <v>1.6463</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2042</v>
+        <v>-2.0672</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-1.2624</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2733</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>0.435</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R6" t="n">
         <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6903</v>
+        <v>0.8841</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6165</v>
+        <v>0.5384</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0738</v>
+        <v>0.3458</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9347</v>
+        <v>-1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. WESTERMANN</t>
+          <t>A. GALAN POZO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7939000000000001</v>
+        <v>0.654</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4949</v>
+        <v>1.112</v>
       </c>
       <c r="F7" t="n">
-        <v>0.299</v>
+        <v>-0.4581</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0074</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4385</v>
+        <v>1.0097</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4312</v>
+        <v>-0.9363</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2758</v>
+        <v>1.8227</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1888</v>
+        <v>1.9741</v>
       </c>
       <c r="L7" t="n">
-        <v>2.087</v>
+        <v>-0.1514</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2832</v>
+        <v>-1.7493</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.6274</v>
+        <v>-0.9643</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6558</v>
+        <v>-0.7849</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8018</v>
+        <v>0.2325</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4817</v>
+        <v>0.0288</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3201</v>
+        <v>0.2037</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7395</v>
+        <v>-0.7395</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. GALAN POZO</t>
+          <t>L. WESTERMANN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1352</v>
+        <v>0.1349</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2612</v>
+        <v>-0.2874</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3964</v>
+        <v>0.4223</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07340000000000001</v>
+        <v>-0.0074</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0097</v>
+        <v>-1.4385</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9363</v>
+        <v>1.4312</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8227</v>
+        <v>2.2758</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9741</v>
+        <v>0.1888</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1514</v>
+        <v>2.087</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7493</v>
+        <v>-2.2832</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9643</v>
+        <v>-1.6274</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7849</v>
+        <v>-0.6558</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0875</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5566</v>
+        <v>1.1428</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.822</v>
+        <v>0.6994</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2653</v>
+        <v>0.4434</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7395</v>
+        <v>0.7395</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="9">
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. KRAVIC</t>
+          <t>M. SPEIGHT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5091</v>
+        <v>-0.7855</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9726</v>
+        <v>-0.752</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4816</v>
+        <v>-0.0335</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1412</v>
+        <v>-0.6113</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9643</v>
+        <v>-0.1642</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8232</v>
+        <v>-0.447</v>
       </c>
       <c r="J10" t="n">
-        <v>2.8714</v>
+        <v>-0.7268</v>
       </c>
       <c r="K10" t="n">
-        <v>2.1447</v>
+        <v>0.0182</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7267</v>
+        <v>-0.7451</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.7302</v>
+        <v>0.1155</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1803</v>
+        <v>-0.1825</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5499</v>
+        <v>0.298</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6525</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5225</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1322</v>
+        <v>-0.1742</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2762</v>
+        <v>-0.0252</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.144</v>
+        <v>-0.149</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. SPEIGHT</t>
+          <t>R. ANDERSSON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8973</v>
+        <v>-1.0951</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8638</v>
+        <v>0.8516</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0335</v>
+        <v>-1.9467</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6113</v>
+        <v>-0.8797</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1642</v>
+        <v>-0.1187</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.447</v>
+        <v>-0.761</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7268</v>
+        <v>1.0895</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0182</v>
+        <v>1.2592</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7451</v>
+        <v>-0.1697</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1155</v>
+        <v>-1.9692</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1825</v>
+        <v>-1.3779</v>
       </c>
       <c r="O11" t="n">
-        <v>0.298</v>
+        <v>-0.5913</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.305</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.286</v>
+        <v>-0.1953</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.137</v>
+        <v>-0.2379</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.149</v>
+        <v>0.0427</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. ANDERSSON</t>
+          <t>D. KRAVIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9189</v>
+        <v>-1.1612</v>
       </c>
       <c r="E12" t="n">
-        <v>0.336</v>
+        <v>1.2587</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2549</v>
+        <v>-2.42</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8797</v>
+        <v>0.1412</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1187</v>
+        <v>0.9643</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.761</v>
+        <v>-0.8232</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0895</v>
+        <v>2.8714</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2592</v>
+        <v>2.1447</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.1697</v>
+        <v>0.7267</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.9692</v>
+        <v>-2.7302</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3779</v>
+        <v>-1.1803</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5913</v>
+        <v>-1.5499</v>
       </c>
       <c r="P12" t="n">
-        <v>1.305</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R12" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.019</v>
+        <v>0.4801</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.5624</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2656</v>
+        <v>-0.0823</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.3252</v>
+        <v>-1.13</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.3252</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.2798</v>
+        <v>-4.3231</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.5785</v>
+        <v>-1.6218</v>
       </c>
       <c r="F13" t="n">
         <v>-2.7013</v>
@@ -1468,10 +1468,10 @@
         <v>0.87</v>
       </c>
       <c r="S13" t="n">
-        <v>0.012</v>
+        <v>-0.0312</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1454</v>
+        <v>-0.1887</v>
       </c>
       <c r="U13" t="n">
         <v>0.1574</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.809100000000001</v>
+        <v>9.494300000000003</v>
       </c>
       <c r="E14" t="n">
-        <v>18.4738</v>
+        <v>19.1587</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.6646</v>
+        <v>-9.6647</v>
       </c>
       <c r="G14" t="n">
         <v>6.0721</v>
@@ -1516,7 +1516,7 @@
         <v>-0.4100999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>6.482500000000002</v>
+        <v>6.4825</v>
       </c>
       <c r="J14" t="n">
         <v>24.6645</v>
@@ -1546,16 +1546,16 @@
         <v>11.9625</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2351</v>
+        <v>2.920100000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3183000000000001</v>
+        <v>1.0034</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9165</v>
+        <v>1.9166</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5857999999999999</v>
+        <v>-0.5857999999999997</v>
       </c>
       <c r="W14" t="n">
         <v>4.366099999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3487</v>
+        <v>3.2774</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5987</v>
+        <v>5.1575</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.25</v>
+        <v>-1.8801</v>
       </c>
       <c r="G15" t="n">
         <v>4.5872</v>
@@ -1624,13 +1624,13 @@
         <v>1.9576</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.6305</v>
+        <v>-0.7018</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8663999999999999</v>
+        <v>-0.3076</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.764</v>
+        <v>-0.3942</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3904</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2678</v>
+        <v>1.4489</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8507</v>
+        <v>3.186</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5829</v>
+        <v>-1.7371</v>
       </c>
       <c r="G16" t="n">
         <v>2.8797</v>
@@ -1702,13 +1702,13 @@
         <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2193</v>
+        <v>-0.0382</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8784</v>
+        <v>-0.5432</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6591</v>
+        <v>0.505</v>
       </c>
       <c r="V16" t="n">
         <v>0.5649999999999999</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0909</v>
+        <v>0.2702</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2601</v>
+        <v>2.1483</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1692</v>
+        <v>-1.8781</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6898</v>
@@ -1780,13 +1780,13 @@
         <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7806999999999999</v>
+        <v>-0.04</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2776</v>
+        <v>0.1658</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5031</v>
+        <v>-0.2058</v>
       </c>
       <c r="V17" t="n">
         <v>0.5649999999999999</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. SMITH</t>
+          <t>O. SIQUIER COSTA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0819</v>
+        <v>0.0577</v>
       </c>
       <c r="E18" t="n">
-        <v>2.7752</v>
+        <v>0.2048</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.8571</v>
+        <v>-0.1471</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7055</v>
+        <v>-0.025</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2468</v>
+        <v>0.0213</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.9523</v>
+        <v>-0.0462</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3571</v>
+        <v>0.093</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9746</v>
+        <v>0.0547</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3825</v>
+        <v>0.0382</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.0626</v>
+        <v>-0.118</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.7278</v>
+        <v>-0.0335</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.3348</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P18" t="n">
         <v>0.2175</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5807</v>
+        <v>-0.1349</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6802</v>
+        <v>0.1118</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.2466</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1745</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.1745</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. SIQUIER COSTA</t>
+          <t>O. MATULIONIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0849</v>
+        <v>-0.5194</v>
       </c>
       <c r="E19" t="n">
-        <v>0.093</v>
+        <v>1.3141</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1779</v>
+        <v>-1.8335</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.025</v>
+        <v>-0.3724</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0213</v>
+        <v>0.8515</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0462</v>
+        <v>-1.224</v>
       </c>
       <c r="J19" t="n">
-        <v>0.093</v>
+        <v>1.4764</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0547</v>
+        <v>1.5329</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0382</v>
+        <v>-0.0566</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.118</v>
+        <v>-1.8488</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0335</v>
+        <v>-0.6814</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-1.1674</v>
       </c>
       <c r="P19" t="n">
         <v>0.2175</v>
@@ -1936,13 +1936,13 @@
         <v>0.2175</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2775</v>
+        <v>-0.3644</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.1622</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2775</v>
+        <v>-0.2022</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. MATULIONIS</t>
+          <t>L. SMITH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6619</v>
+        <v>-0.6908</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2024</v>
+        <v>2.1047</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8643</v>
+        <v>-2.7954</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3724</v>
+        <v>-0.7055</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8515</v>
+        <v>1.2468</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.224</v>
+        <v>-1.9523</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4764</v>
+        <v>3.3571</v>
       </c>
       <c r="K20" t="n">
-        <v>1.5329</v>
+        <v>2.9746</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0566</v>
+        <v>0.3825</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8488</v>
+        <v>-4.0626</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6814</v>
+        <v>-1.7278</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1674</v>
+        <v>-2.3348</v>
       </c>
       <c r="P20" t="n">
         <v>0.2175</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.507</v>
+        <v>-0.0282</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.274</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.233</v>
+        <v>-0.0379</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.1745</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.1745</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8752</v>
+        <v>-1.8213</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8925999999999999</v>
+        <v>0.6691</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7678</v>
+        <v>-2.4904</v>
       </c>
       <c r="G21" t="n">
         <v>-1.8362</v>
@@ -2092,13 +2092,13 @@
         <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0035</v>
+        <v>0.0574</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3461</v>
+        <v>0.1226</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3426</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-1.13</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1039</v>
+        <v>-2.2001</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5927</v>
+        <v>-0.2574</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5112</v>
+        <v>-1.9427</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9585</v>
@@ -2170,13 +2170,13 @@
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1798</v>
+        <v>0.0835</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0154</v>
+        <v>-0.6801</v>
       </c>
       <c r="U22" t="n">
-        <v>1.1952</v>
+        <v>0.7637</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1952</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1984</v>
+        <v>-3.4104</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1861</v>
+        <v>-2.5213</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0123</v>
+        <v>-0.8891</v>
       </c>
       <c r="G23" t="n">
         <v>-1.005</v>
@@ -2248,13 +2248,13 @@
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0257</v>
+        <v>-0.1863</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2776</v>
+        <v>-0.0577</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2519</v>
+        <v>-0.1286</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9141</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5105</v>
+        <v>-5.2215</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2295</v>
+        <v>-2.3412</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.281</v>
+        <v>-2.8803</v>
       </c>
       <c r="G24" t="n">
         <v>-5.9466</v>
@@ -2326,13 +2326,13 @@
         <v>1.5225</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1713</v>
+        <v>-0.8823</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4638</v>
+        <v>-0.5756</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7074</v>
+        <v>-0.3067</v>
       </c>
       <c r="V24" t="n">
         <v>2.2599</v>
@@ -2362,13 +2362,13 @@
         <v>-8.8093</v>
       </c>
       <c r="E25" t="n">
-        <v>9.664400000000001</v>
+        <v>9.664599999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>-18.4737</v>
+        <v>-18.4738</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.072099999999999</v>
+        <v>-6.0721</v>
       </c>
       <c r="H25" t="n">
         <v>0.4102000000000006</v>
@@ -2383,7 +2383,7 @@
         <v>11.711</v>
       </c>
       <c r="L25" t="n">
-        <v>6.880999999999999</v>
+        <v>6.881</v>
       </c>
       <c r="M25" t="n">
         <v>-24.6644</v>
@@ -2407,10 +2407,10 @@
         <v>-2.2352</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.9165</v>
+        <v>-1.9166</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3185000000000001</v>
+        <v>-0.3184999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>0.5857000000000001</v>
